--- a/08.07.2026/JIRA-UserStory7-KunalMaheshwari(85010944).xlsx
+++ b/08.07.2026/JIRA-UserStory7-KunalMaheshwari(85010944).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0377cb67aaf17726/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0377cb67aaf17726/Documents/GitHub/Kunal-Testing-Assignments/08.07.2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="8_{8E420B2E-1779-49C8-8847-19CA0911E55C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF7683B1-9775-49CC-9240-EA0F4D876ED5}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="8_{8E420B2E-1779-49C8-8847-19CA0911E55C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FA88814-CB03-4FA1-87F1-386126F32CEE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{5EFC1ECA-346A-44C7-A537-235ED04AC679}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{5EFC1ECA-346A-44C7-A537-235ED04AC679}"/>
   </bookViews>
   <sheets>
     <sheet name="JIRA-UserStory-TestScenarios" sheetId="1" r:id="rId1"/>
@@ -2176,7 +2176,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2342,10 +2342,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2375,7 +2375,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2720,16 +2720,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17918D4B-BCDA-4A26-8843-549C72496C22}">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -2738,28 +2738,28 @@
       <c r="D1" s="17"/>
       <c r="E1" s="17"/>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
       <c r="D2" s="17"/>
       <c r="E2" s="17"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
       <c r="E3" s="17"/>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
         <v>1</v>
       </c>
@@ -2768,14 +2768,14 @@
       <c r="D5" s="17"/>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>2</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="78.75" customHeight="1">
+    <row r="8" spans="1:5" ht="78.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="55.15">
+    <row r="9" spans="1:5" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -2826,7 +2826,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="55.15">
+    <row r="10" spans="1:5" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="41.45">
+    <row r="11" spans="1:5" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="41.45">
+    <row r="12" spans="1:5" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="55.15">
+    <row r="13" spans="1:5" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>30</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="55.15">
+    <row r="14" spans="1:5" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>35</v>
       </c>
@@ -2911,7 +2911,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="41.45">
+    <row r="15" spans="1:5" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>39</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="41.45">
+    <row r="16" spans="1:5" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>44</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="55.15">
+    <row r="17" spans="1:5" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>49</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="55.15">
+    <row r="18" spans="1:5" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>54</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="69">
+    <row r="19" spans="1:5" ht="69" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>59</v>
       </c>
@@ -2996,7 +2996,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="55.15">
+    <row r="20" spans="1:5" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>63</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="41.45">
+    <row r="21" spans="1:5" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>68</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="27.6">
+    <row r="22" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>73</v>
       </c>
@@ -3059,20 +3059,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7170A79-1C06-4BCF-A325-1895AED3C023}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="5" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.6640625" customWidth="1"/>
+    <col min="5" max="5" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>78</v>
       </c>
@@ -3084,7 +3087,7 @@
       <c r="G1" s="14"/>
       <c r="H1" s="14"/>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>79</v>
       </c>
@@ -3098,7 +3101,7 @@
       <c r="G2" s="15"/>
       <c r="H2" s="15"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>81</v>
       </c>
@@ -3112,7 +3115,7 @@
       <c r="G3" s="15"/>
       <c r="H3" s="15"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>83</v>
       </c>
@@ -3126,7 +3129,7 @@
       <c r="G4" s="16"/>
       <c r="H4" s="16"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>85</v>
       </c>
@@ -3138,7 +3141,7 @@
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>86</v>
       </c>
@@ -3150,7 +3153,7 @@
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>87</v>
       </c>
@@ -3162,7 +3165,7 @@
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -3172,7 +3175,7 @@
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>88</v>
       </c>
@@ -3198,7 +3201,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="208.9" customHeight="1">
+    <row r="10" spans="1:8" ht="208.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>96</v>
       </c>
@@ -3224,7 +3227,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="161.44999999999999" customHeight="1">
+    <row r="11" spans="1:8" ht="161.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>103</v>
       </c>
@@ -3250,7 +3253,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="169.15" customHeight="1">
+    <row r="12" spans="1:8" ht="169.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>109</v>
       </c>
@@ -3276,7 +3279,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="162.6" customHeight="1">
+    <row r="13" spans="1:8" ht="162.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>115</v>
       </c>
@@ -3302,7 +3305,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="187.5" customHeight="1">
+    <row r="14" spans="1:8" ht="187.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>121</v>
       </c>
@@ -3328,7 +3331,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="145.15" customHeight="1">
+    <row r="15" spans="1:8" ht="145.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>127</v>
       </c>
@@ -3354,7 +3357,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="129.75" customHeight="1">
+    <row r="16" spans="1:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>133</v>
       </c>
@@ -3380,7 +3383,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="120.6" customHeight="1">
+    <row r="17" spans="1:8" ht="120.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>138</v>
       </c>
@@ -3406,7 +3409,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="121.9" customHeight="1">
+    <row r="18" spans="1:8" ht="121.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>143</v>
       </c>
@@ -3432,7 +3435,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="148.9" customHeight="1">
+    <row r="19" spans="1:8" ht="148.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>147</v>
       </c>
@@ -3458,7 +3461,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="145.15" customHeight="1">
+    <row r="20" spans="1:8" ht="145.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>152</v>
       </c>
@@ -3484,7 +3487,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="128.44999999999999" customHeight="1">
+    <row r="21" spans="1:8" ht="128.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>158</v>
       </c>
@@ -3510,7 +3513,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="136.15" customHeight="1">
+    <row r="22" spans="1:8" ht="136.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>164</v>
       </c>
@@ -3536,7 +3539,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="124.15" customHeight="1">
+    <row r="23" spans="1:8" ht="124.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>169</v>
       </c>
@@ -3562,7 +3565,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="187.9" customHeight="1">
+    <row r="24" spans="1:8" ht="187.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>174</v>
       </c>
@@ -3605,22 +3608,22 @@
     <hyperlink ref="E12" r:id="rId1" display="mailto:raghu.astepahead@gmail.com" xr:uid="{B51ABAAE-120C-4D2E-9E4D-3DF627BF1682}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="92" fitToHeight="0" orientation="landscape" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91FCC20A-3E8C-4207-AD06-466A25E7785B}">
   <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.45" customHeight="1">
+    <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -3629,28 +3632,28 @@
       <c r="D1" s="19"/>
       <c r="E1" s="11"/>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="20"/>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
       <c r="D2" s="21"/>
       <c r="E2" s="11"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="22"/>
       <c r="B3" s="23"/>
       <c r="C3" s="23"/>
       <c r="D3" s="23"/>
       <c r="E3" s="11"/>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>180</v>
       </c>
@@ -3664,7 +3667,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="41.45">
+    <row r="6" spans="1:5" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>96</v>
       </c>
@@ -3678,7 +3681,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="27.6">
+    <row r="7" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>103</v>
       </c>
@@ -3692,7 +3695,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="27.6">
+    <row r="8" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>109</v>
       </c>
@@ -3706,7 +3709,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="27.6">
+    <row r="9" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>115</v>
       </c>
@@ -3720,7 +3723,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="41.45">
+    <row r="10" spans="1:5" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>121</v>
       </c>
@@ -3734,7 +3737,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="41.45">
+    <row r="11" spans="1:5" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>127</v>
       </c>
@@ -3748,7 +3751,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="27.6">
+    <row r="12" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>133</v>
       </c>
@@ -3762,7 +3765,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="27.6">
+    <row r="13" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>138</v>
       </c>
@@ -3776,7 +3779,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="27.6">
+    <row r="14" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>143</v>
       </c>
@@ -3790,7 +3793,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="27.6">
+    <row r="15" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>147</v>
       </c>
@@ -3804,7 +3807,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="41.45">
+    <row r="16" spans="1:5" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>152</v>
       </c>
@@ -3818,7 +3821,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="27.6">
+    <row r="17" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>158</v>
       </c>
@@ -3832,7 +3835,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="41.45">
+    <row r="18" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>164</v>
       </c>
@@ -3846,7 +3849,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="41.45">
+    <row r="19" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>169</v>
       </c>
@@ -3860,7 +3863,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="27.6">
+    <row r="20" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>174</v>
       </c>
